--- a/inventory/files/2026-W42/STA_US_LEGACY_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_US_LEGACY_2026-W42.xlsx
@@ -1536,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="28" min="1" max="1"/>
@@ -1692,57 +1692,57 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C-148TA</t>
+          <t>C-246TA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C-102TA</t>
+          <t>C-7600PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C-246TA</t>
+          <t>C-148TA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H-148TA</t>
+          <t>C-102TA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C-7600PA</t>
+          <t>H-148TA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -1752,63 +1752,63 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H-146P</t>
+          <t>C-192TA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C-192TA</t>
+          <t>C-244TA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C-297T</t>
+          <t>H-146P</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C-298T</t>
+          <t>C-163T</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SE-146</t>
+          <t>H-109TA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C-7300T</t>
+          <t>C-297T</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1818,67 +1818,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C-163T</t>
+          <t>C-298T</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H-261P</t>
+          <t>SE-146</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H-217T</t>
+          <t>C-7300T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H-TOP3KITA</t>
+          <t>H-261P</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C-244TA</t>
+          <t>H-217T</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H-190Q</t>
+          <t>C-102Q</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C-102Q</t>
+          <t>H-190Q</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1888,17 +1888,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H-109TA</t>
+          <t>H-144P</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>H-144P</t>
+          <t>H-305T</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1908,7 +1908,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>H-305T</t>
+          <t>H-112T</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1918,7 +1918,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H-112T</t>
+          <t>C-211P</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1928,7 +1928,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C-211P</t>
+          <t>H-264P</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1938,7 +1938,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>H-212T</t>
+          <t>H-200T</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1948,7 +1948,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>H-264P</t>
+          <t>H-256T</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1958,7 +1958,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>H-200T</t>
+          <t>H-247T</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1968,7 +1968,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>H-256T</t>
+          <t>FX-106A</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1978,30 +1978,10 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>H-310T</t>
+          <t>C-242P</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>H-247T</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>FX-106A</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
         <v>3</v>
       </c>
     </row>
